--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92565432273</v>
+        <v>46157.93088311848</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93088311848</v>
+        <v>46157.93166753213</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93166753213</v>
+        <v>46157.93397419228</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93397419228</v>
+        <v>46157.93715087497</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93715087497</v>
+        <v>46158.28213829558</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28213829558</v>
+        <v>46158.29675151428</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29675151428</v>
+        <v>46158.29811776606</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29811776606</v>
+        <v>46158.33384687286</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33384687286</v>
+        <v>46158.36854026929</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/30. ЯмалЭкология (вывоз мусора)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36854026929</v>
+        <v>46158.372848213</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
